--- a/CodeSystem-ACCESSReportDataResultCS.xlsx
+++ b/CodeSystem-ACCESSReportDataResultCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSReportDataResultCS.xlsx
+++ b/CodeSystem-ACCESSReportDataResultCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSReportDataResultCS.xlsx
+++ b/CodeSystem-ACCESSReportDataResultCS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>7</t>
+    <t>6</t>
   </si>
   <si>
     <t>Level</t>
@@ -151,15 +151,6 @@
   </si>
   <si>
     <t>The data reporting submission was successful.</t>
-  </si>
-  <si>
-    <t>validation-error</t>
-  </si>
-  <si>
-    <t>Validation error</t>
-  </si>
-  <si>
-    <t>Data submission failed validation (see the 'issues' parameter for specific errors and details).</t>
   </si>
   <si>
     <t>duplicate</t>
@@ -516,7 +507,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -617,20 +608,6 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>63</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CodeSystem-ACCESSReportDataResultCS.xlsx
+++ b/CodeSystem-ACCESSReportDataResultCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSReportDataResultCS.xlsx
+++ b/CodeSystem-ACCESSReportDataResultCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
